--- a/docs/FEATURE_REGISTER.xlsx
+++ b/docs/FEATURE_REGISTER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to read this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$1:$G$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$1:$H$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,6 +117,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,16 +492,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -508,25 +518,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Sub-feature</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Requirement type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
@@ -538,30 +553,35 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>Workspace &amp; tenancy</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
           <t>Multi-tenant workspaces</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Every customer gets an isolated workspace (Tenant). Projects, users, integrations, runs and artifacts all live under one tenant, and a tenant can carry its own model-routing config.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>All state lives in the platform database, per tenant.</t>
         </is>
@@ -573,30 +593,35 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
+          <t>Workspace &amp; tenancy</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
           <t>Tenant isolation enforced in the database (RLS)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Every table carries tenant_id and a Postgres row-level-security policy, set per request and per background activity, so one tenant can never read another tenant's rows even if application code is wrong.</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Locked architecture decision; proved by DB-level isolation tests on each table.</t>
         </is>
@@ -608,30 +633,35 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Accounts, sign-in &amp; invitations</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
           <t>Self-serve sign up</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>A new customer signs up with name, email, password and organisation name; the workspace and its first admin are created together and the user is logged straight in.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Session-based; the workspace comes from the signed-in user, not a header.</t>
         </is>
@@ -643,30 +673,35 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
+          <t>Accounts, sign-in &amp; invitations</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
           <t>Log in / log out / current user</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Server-session login, logout, and a 'me' endpoint returning the signed-in user, their workspace and their per-project role memberships. The UI is auth-gated and redirects to login.</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -674,30 +709,35 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>Accounts, sign-in &amp; invitations</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
           <t>Invite users by email</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>An admin invites a person by email, optionally pre-assigning project roles. Invitations can be resent (rotating the token) or revoked, and expire after 7 days.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Raw token is emailed only, never returned by the API.</t>
         </is>
@@ -709,30 +749,35 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
+          <t>Accounts, sign-in &amp; invitations</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
           <t>Accept an invitation</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>The invitee opens the emailed link, previews who invited them, sets a password, and lands with their queued project memberships already granted.</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -740,30 +785,35 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>Accounts, sign-in &amp; invitations</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
           <t>Forgot / reset password</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Self-serve password reset by single-use emailed token with a 1-hour expiry; the request endpoint never reveals whether an address exists.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -771,30 +821,35 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>Roles &amp; permissions</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
           <t>Workspace admins</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>A tenant-wide admin flag, toggleable per user, with a guard that the last admin can never be removed or demote themselves out of the workspace.</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -802,30 +857,35 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>Roles &amp; permissions</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
           <t>Project roles and memberships</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Users are granted per-project roles (product owner, architect, tech lead, reviewer, QA lead, designer, DevOps, security engineer, engineer, project admin). Roles decide who may approve which gate.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -833,30 +893,35 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>Roles &amp; permissions</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
           <t>Role coverage report</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>A per-project matrix showing which gate roles have holders and which do not, flagging where an unassigned role would leave a gate with nobody able to decide it.</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Seen live: ticks for covered roles and crosses for uncovered ones, each carrying the advisory 'an admin can approve this gate' note.</t>
         </is>
@@ -868,30 +933,35 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>Roles &amp; permissions</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
           <t>Admin gate fallback</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>A project admin or workspace admin can approve any gate, so a missing specialist role never deadlocks the pipeline.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -899,30 +969,35 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>Roles &amp; permissions</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
           <t>Admin-only route protection</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Deep-linking to an admin screen as a non-admin shows a clear 'admin access needed' page instead of a blank or broken render.</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -930,30 +1005,35 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>Projects &amp; configuration</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
           <t>Create a project</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Create a project choosing greenfield (from scratch) or brownfield (existing codebase) and its repository topology. Project names are unique within a workspace.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -961,30 +1041,35 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>Projects &amp; configuration</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
           <t>Project profile editor</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>The project's own description of itself — domain, tech stack, conventions, theme tokens, preview start command, export policy — which is what the agents are briefed from.</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Seen live: description, domain, tech stack, coding standards, NFRs, constraints, glossary, important context. Versioned on every save.</t>
         </is>
@@ -996,30 +1081,35 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>Projects &amp; configuration</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
           <t>Per-project theming</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Design tokens, brand and responsive breakpoints stored on the project profile and passed verbatim into the agent brief, so design output matches the client's system without forking any code.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1027,30 +1117,35 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
+          <t>Projects &amp; configuration</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
           <t>Multiple repositories per project</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>One project can hold N repositories (e.g. front end and back end) with roles and default branches; adding or removing one keeps the project's topology (single / split / multi) correct, and one repo is the default.</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1058,30 +1153,35 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>Integrations &amp; connections</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
           <t>Integrations grid</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>An admin screen listing every capability the platform can connect (document store, task tracker, code host, design source, test management, code intelligence, accessibility AI) with its connection state.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Seen live: six capability cards. The accessibility-AI capability is registered in the backend but is not one of them.</t>
         </is>
@@ -1093,30 +1193,35 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>Integrations &amp; connections</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
           <t>Connect a capability with stored secrets</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>A connect form that stores credentials encrypted and write-only — they are never echoed back in any API response; the UI only ever shows whether a capability is configured.</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Vault/token-broker hardening is a later phase.</t>
         </is>
@@ -1128,30 +1233,35 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>Integrations &amp; connections</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
           <t>Test a connection</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>A test-connection action per integration that checks the chosen vendor is wired and a credential is stored, and records the result as the connection's health.</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Live reachability check is deferred to hardening.</t>
         </is>
@@ -1163,30 +1273,35 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>Integrations &amp; connections</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
           <t>CI ingest tokens</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Per-project tokens for a client's CI to post results back to the platform: issue (secret shown once), list, and revoke. The token hash only is stored.</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1194,30 +1309,35 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>Integrations &amp; connections</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
           <t>Per-phase export policy</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Which external system each phase's artifacts may be exported to, as a locked default mapping with per-project overrides. Gate approval never auto-exports; export is always a deliberate user action.</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1225,30 +1345,35 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
           <t>Work items as the unit of work</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Epics, stories, tasks and defects with parent/child relationships, cross-repo dependencies and a repo assignment. Work is a per-work-item graph, not a fixed linear pipeline.</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1256,30 +1381,35 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
           <t>Work items board</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Board and list views of a project's work with filters by level, phase and parent, showing owner, phase, artifact count and what each item needs next.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Seen live with 252 items: board and list views, search, and phase / level / role / status filters. The list renders every row at once, with no pagination.</t>
         </is>
@@ -1291,30 +1421,35 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
           <t>Type-adaptive lifecycle rail</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>The work item detail screen shows a different lifecycle for each level: planning phases for an epic, build-and-review loop for a task, remediation for a defect — so a task never shows phases that do not apply to it.</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
           <t>Built - partial</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>Seen live: the caption adapts (Epic 'plan tier' vs Task 'build tier'), but both render the same 12 phase nodes and every node read 'Upcoming' on completed work. The rail is labelled type-adaptive, not yet drawn that way.</t>
         </is>
@@ -1326,30 +1461,35 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
           <t>Edit a work item</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Change a work item's title, description or level from the detail screen.</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1357,30 +1497,35 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
           <t>Cancel a work item</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Close work that is never going to be built, from the list or the detail screen, without having to invent a fake completion.</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1388,30 +1533,35 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
           <t>Phase catalog and trigger picker</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>The list of lifecycle phases available per tier, with a per-phase flag for whether it can be triggered on this item right now — what the trigger picker renders.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -1419,30 +1569,35 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
           <t>Trigger a phase</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Start an agent run for a phase on a work item. The run is attributed to the signed-in user and routed to that user's own connected machine when they have one.</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1450,30 +1605,35 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
           <t>Runs list and live run console</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Every run with its phase, status, cost and timeline; the console streams the run's events live and covers all of its states (queued, running, waiting on an answer, waiting on a gate, failed, taken over, complete).</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -1481,30 +1641,35 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
           <t>Run transcript</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>A readable transcript of what an agent actually did in a run — turn by turn — for audit and for understanding a result.</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
           <t>Built - no data recorded</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Seen live: screen and endpoint work, but 25 runs checked (incl. completed ones) all returned zero turns. The reader looks for run.outputs['transcript']; nothing in the runner or driver ever writes it.</t>
         </is>
@@ -1516,30 +1681,35 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
           <t>Event ledger</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>An append-only record of everything that happened to a run, work item or artifact, used for provenance, the console timeline, and reconstructing history.</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -1547,30 +1717,35 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
           <t>Human takeover</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>A person can take a work item or run away from the agent and finish it by hand; automation pauses on that item and the takeover is recorded.</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Seen live on the recovery screen: a genuinely parked run offering Reconnect and re-run, Take over manually, or Connect your machine.</t>
         </is>
@@ -1582,30 +1757,35 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
           <t>Resume a run</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Restart a run that stopped — an offline machine, a hit usage limit, an engine error — without losing the work already recorded.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Seen live: 'Reconnect and re-run' on a parked implementation run, with the promise that nothing was published and answered questions are remembered.</t>
         </is>
@@ -1617,30 +1797,35 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
           <t>Offline takeover / recovery screen</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>One screen listing runs that stalled because the machine went offline or a report never arrived, with the actions to take over or resume each one.</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1648,30 +1833,35 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
           <t>Stranded-run detection</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Background checks that notice when a run says it is still going but its workflow has already ended, and when an audit was judged but never finished, so nothing sits silently stuck.</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Added after two live incidents.</t>
         </is>
@@ -1683,30 +1873,35 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
+          <t>Planning agents</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
           <t>Ideation agent (01)</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Turns a raw idea into a structured concept: problem, users, value, scope boundaries and success measures. Gate: product owner.</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Reasoning migrated verbatim from the v6 suite.</t>
         </is>
@@ -1718,30 +1913,35 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
+          <t>Planning agents</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
           <t>Requirements agent (02)</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Produces functional and non-functional requirements with acceptance criteria and traceability back to the concept. Gate: product owner.</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -1749,30 +1949,35 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>Planning agents</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
           <t>PRD agent (03)</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Writes the product requirements document from the approved requirements. Gate: product owner.</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1780,30 +1985,35 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
+          <t>Planning agents</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
           <t>Architecture agent (04)</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Produces the system architecture, data model, API spec and technology decisions. Gate: architect.</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -1811,30 +2021,35 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>Planning agents</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
           <t>UX design agent (05)</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Produces user journeys, wireframes with every state, and a design system — or reads the client's existing Figma as the source of truth instead of generating. Gate: designer.</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>Read-as-source-of-truth and generate modes.</t>
         </is>
@@ -1846,30 +2061,35 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
+          <t>Planning agents</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
           <t>Task breakdown agent (06)</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Turns the PRD and architecture into a proposed backlog of epics, stories and tasks with dependencies and a definition of done. Gate: tech lead.</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Approved backlog reconciles into Jira.</t>
         </is>
@@ -1881,30 +2101,35 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
           <t>Implementation agent (07)</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Writes the code for a work item in a managed git worktree on the developer's machine, following clean-code and TDD discipline, and handles remediation rounds. Gate: tech lead.</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>The platform, not the agent, commits and opens the PR.</t>
         </is>
@@ -1916,30 +2141,35 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
           <t>Code review agent (08)</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Reviews the pull request diff across eleven dimensions including OWASP issues and performance, returning severity-tiered findings that drive the remediation loop. Gate: reviewer.</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -1947,30 +2177,35 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
           <t>Testing agent (09)</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Authors the test strategy and test cases against requirements — functional, performance, security smoke and accessibility — with a traceability map and coverage floors. Gate: QA lead.</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -1978,30 +2213,35 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
           <t>Test automation agent (09b)</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Writes runnable automation from a test case, discovering real locators against the running app with a browser tool rather than guessing them, using the page-object pattern. Gate: QA lead.</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Runs against a live preview of the app.</t>
         </is>
@@ -2013,30 +2253,35 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
           <t>Accessibility judge agent (09c)</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Judges captured screens against WCAG success criteria that no rule engine can decide, returning a verdict and a confidence per element.</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>Platform-native agent; no legacy equivalent.</t>
         </is>
@@ -2048,30 +2293,35 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
           <t>Accessibility journey agent (09d)</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Walks a user journey with the keyboard and reports what only happens in use: focus traps, focus visibility, changes on focus or input, and whether status messages are announced.</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
           <t>Built - not exercised live</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Seen live only in its empty state. Advisory by design; no journey run has ever happened.</t>
         </is>
@@ -2083,30 +2333,35 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
           <t>Security agent (10)</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Reviews the code and dependencies across nine tracks — static analysis, dependencies and licences, SBOM, OWASP Top 10, authn/authz, data, infrastructure, cloud benchmarks and threat modelling. Gate: security engineer.</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2114,30 +2369,35 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
           <t>CI/CD agent (11)</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Generates the pipeline for the project — container build, CI stages, coverage gate, credentials handling — as real files in the repository. Gate: DevOps.</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -2145,30 +2405,35 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
           <t>Deployment agent (12)</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Produces the release plan: readiness checklist, blue-green or canary strategy, smoke tests, monitoring window and rollback runbook. Gate: DevOps.</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
           <t>Built - planning only</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Produces the documents; the platform does not itself deploy or monitor.</t>
         </is>
@@ -2180,30 +2445,35 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
+          <t>Onboarding &amp; analysis agents</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
           <t>Onboarding agent (00)</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Full brownfield onboarding: discovers what already exists across the connected tools and the code, registers it without recreating it, fills gaps, and reports which lifecycle phase to resume from. Gate: product owner.</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -2211,30 +2481,35 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
+          <t>Onboarding &amp; analysis agents</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
           <t>Context bridge agent (00b)</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Extracts the API contract, shared data models and the business rules the back end must enforce, from the code itself, and publishes them as one versioned contract. Gate: architect.</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2242,30 +2517,35 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
+          <t>Onboarding &amp; analysis agents</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
           <t>Codebase intelligence agent (00c)</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Analyses an existing repository — hotspots, dependency graph, dead code, complexity, ownership, decision history — and registers the analysis as project memory. Gate: tech lead.</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -2273,30 +2553,35 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
+          <t>Onboarding &amp; analysis agents</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
           <t>Document vision agent (00e)</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Reads the page images of an uploaded specification, so diagrams and screenshots in a Word or PDF document are not silently lost during onboarding.</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Platform-native agent; no legacy equivalent.</t>
         </is>
@@ -2308,30 +2593,35 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
+          <t>Agent orchestration &amp; engine</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
           <t>Agent registry and per-phase model routing</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Every agent is registered with its phase, gate role, recommended engine and model; a workspace can re-route models without touching agent bodies.</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -2339,30 +2629,35 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
+          <t>Agent orchestration &amp; engine</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
           <t>Durable agent runs</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Every agent run is a durable workflow that survives restarts, is idempotent on replay, and picks up where it left off rather than starting over.</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>Temporal.</t>
         </is>
@@ -2374,30 +2669,35 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
+          <t>Agent orchestration &amp; engine</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
           <t>Build workflow with review and remediation loop</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>A build phase runs end to end: worktree → local build and tests → branch and draft PR → automated review → remediation rounds until nothing blocking remains → human merge gate → merge.</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Seen live in one run's event log: triggered - dispatched - code registered - PR opened - review dispatched - reported - reviewed (cycle 4) - merged - published.</t>
         </is>
@@ -2409,30 +2709,35 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
+          <t>Agent orchestration &amp; engine</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
           <t>Engine abstraction</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>All engine calls go through one execution-driver interface, with the Claude driver as the default, so business logic never talks to a model vendor directly.</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>Other engines are a later phase.</t>
         </is>
@@ -2444,30 +2749,35 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
           <t>Connect your machine (companion runner)</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>A developer enrols their own machine against a project and gets a one-time token; only the hash is kept. The screen shows the setup checklist and live connected/offline status.</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Seen live: connected state, last-seen, disconnect, and a live Ready/Offline pill in the top bar and sidebar.</t>
         </is>
@@ -2479,30 +2789,35 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
           <t>Runs on the developer's own Claude Code</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Planning, review and build phases all execute on the enrolled machine using the developer's own logged-in Claude Code session, not a server API key.</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>Seen live: Connect Machine reads 'Connected - your machine - last seen just now', and states plainly that no API key is used and nothing is billed to the workspace.</t>
         </is>
@@ -2514,30 +2829,35 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
           <t>Companion daemon</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>A background process on the developer's machine that claims work — plan, review, build, code intelligence, accessibility audit — runs it locally and reports the result back.</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -2545,30 +2865,35 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
           <t>Managed git worktrees</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>The platform provisions a clean feature branch worktree per work item, injects secrets as environment variables, and tears it down afterwards, so code is built and tested locally before any PR.</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -2576,30 +2901,35 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
           <t>Remote platform state for the runner</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>The agent on the developer's machine reads and writes platform state through a tenant-bound server endpoint with a tool allowlist — no database credentials ever reach the developer's machine.</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -2607,30 +2937,35 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
+          <t>Agent context &amp; briefing</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
           <t>Platform-state tool server (MCP)</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>The tool surface agents use to read context, fetch artifacts, register artifacts, create work items, add traceability edges and log events.</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -2638,30 +2973,35 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
+          <t>Agent context &amp; briefing</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
           <t>Manifest composer</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Builds the brief an agent receives for a run — project, repository, current work item, answered questions, relevant artifacts, retrieved knowledge, rules — in a fixed order and within a token budget.</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -2669,30 +3009,35 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
+          <t>Agent context &amp; briefing</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
           <t>Per-repository brief scoping</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>On a multi-repo project, a run targeting one repository sees that repository's artifacts plus project-wide ones and the shared API contract; the registry and knowledge index stay shared across repos.</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2700,30 +3045,35 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
+          <t>Clarifications</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
           <t>Agents can ask a human a question</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>An agent that is missing information opens a question in the app and waits. The wait costs nothing — the model is idle — and the answer resumes the run.</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>Seen live: real sessions of up to 12 questions, tiered 'Tier 1 - must answer', answered by a person and replayed back into the run.</t>
         </is>
@@ -2735,30 +3085,35 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
+          <t>Clarifications</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
           <t>Clarifications screen</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>The answering surface: pending questions per run with the right input for each kind (free text, choice, confirm), plus a history of what was already answered.</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>Seen live: needs-answer queue plus a searchable, filterable, paginated history of answered questions.</t>
         </is>
@@ -2770,30 +3125,35 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
+          <t>Clarifications</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
           <t>Answers are never asked twice</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Answered questions are replayed into the next brief and re-asks are matched to the original question, so a crashed or re-dispatched run never re-prompts the human.</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -2801,30 +3161,35 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
+          <t>Run safety &amp; guardrails</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
           <t>Secret scanning before push</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>The worktree is scanned for credentials after a build; a hit blocks the push, fails the build for triage, and the value is redacted rather than echoed.</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -2832,30 +3197,35 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
+          <t>Run safety &amp; guardrails</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
           <t>Network egress allowlist</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>A build may only reach the tenant's code host, the model API, the platform and declared registries; everything else, including the cloud metadata address, is denied.</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -2863,30 +3233,35 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
+          <t>Run safety &amp; guardrails</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
           <t>Per-phase tool allowlist</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Each phase is given only the tools it needs; a build phase cannot call the code host or the network, and the browser surface is granted to test automation only.</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -2894,30 +3269,35 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
+          <t>Run safety &amp; guardrails</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
           <t>Browser tooling for locator discovery</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Test automation gets a curated headless browser tool surface — navigate, snapshot, interact — scoped to the preview app's own origin, so it can find real locators without arbitrary network access.</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -2925,30 +3305,35 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
           <t>Preview environment for the app under test</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>The companion starts the project's own app from a per-repo start command, waits for it to be ready, hands the agent its address, records it against the PR, and tears it down afterwards.</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -2956,30 +3341,35 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
           <t>Companion liveness and worker version guard</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Heartbeats keep a busy machine showing as online, and a worker running old code stands down rather than serving stale behaviour alongside a newer one.</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>Both added after live incidents.</t>
         </is>
@@ -2991,30 +3381,35 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
           <t>Run cost and token accounting</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Each run records its token usage and cost, visible on the run and rolled up on the dashboard.</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
           <t>Built - partial</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>Seen live: cost_usd was null on completed build runs and is shown on no screen. It is populated on the planning/phase-report path only.</t>
         </is>
@@ -3026,30 +3421,35 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
+          <t>Review gates</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
           <t>Human review gates</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Every phase ends at an approval owned by a named role. Nothing publishes and nothing reaches a system of record until a person approves it.</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>Seen live: 3 pending merge gates and a long approved history, each naming the required role.</t>
         </is>
@@ -3061,30 +3461,35 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
+          <t>Review gates</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
           <t>Gates screen with history</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>The pending gate queue with the artifacts under review, the decision actions, and the record of past decisions and who made them.</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>Seen live: pending queue + decided history with filters. Three actions, not two — Approve, Request changes, Reject — and decisions are stamped with name and role.</t>
         </is>
@@ -3096,30 +3501,35 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
+          <t>Review gates</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
           <t>Criteria checklist gates</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>A gate can carry a checklist of conditions — the WCAG criteria on a design gate, for example — and cannot be approved while any required condition is unmet.</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>Seen live: the screen renders and correctly reports 'this gate has no checklist' on a merge gate. Only design gates carry WCAG criteria, and none was open to observe.</t>
         </is>
@@ -3131,30 +3541,35 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
+          <t>Artifacts &amp; publishing</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
           <t>Draft to published artifact lifecycle</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Artifacts are registered as drafts, reviewed, gated, and only then published. Rejection leaves them as drafts; no agent can auto-publish.</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>Seen live: three states in the registry — Draft, Staged, Published. The Export action appears only on published rows.</t>
         </is>
@@ -3166,30 +3581,35 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
+          <t>Artifacts &amp; publishing</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
           <t>Artifact registry</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>The index of every artifact the platform knows about: pointers, content hashes, versions, provenance and system-of-record links — never the artifact body as the source of truth.</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -3197,30 +3617,35 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
+          <t>Artifacts &amp; publishing</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
           <t>Artifact preview</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Read-through preview of an artifact's rendered body — from platform storage for internal drafts, live from Confluence or Jira for published ones, or a deep link where the body lives elsewhere.</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>Seen live: rendered markdown behind a 'read-through, never an editor' banner, with the version history beside it.</t>
         </is>
@@ -3232,30 +3657,35 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
+          <t>Artifacts &amp; publishing</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
           <t>Artifact version history</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Earlier revisions of an artifact listed newest first, so a reviewer can see what changed between runs.</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <t>A true per-artifact version counter exists only for the API contract.</t>
         </is>
@@ -3267,30 +3697,35 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
+          <t>Artifacts &amp; publishing</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
           <t>Manual export / publish to the tool of record</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>An approved artifact is pushed to Confluence, Jira or Xray on a deliberate user action, governed by the export policy, and re-publishing updates the same page or issue instead of duplicating it.</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>Seen live: the publish dialog checks gate approval first and says which target the project's export policy allows.</t>
         </is>
@@ -3302,30 +3737,35 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
+          <t>Traceability &amp; knowledge</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
           <t>Traceability graph</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Requirement → PRD → epic → story → code → test lineage, rendered as a navigable graph with deep links into the external tools.</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t>Seen live: a populated graph across 370 artifacts of 33 types, colour-keyed published / pending gate / draft.</t>
         </is>
@@ -3337,30 +3777,35 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
+          <t>Traceability &amp; knowledge</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
           <t>Project knowledge index</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>Artifacts and code intelligence are indexed for retrieval and blended into the agent brief; keyword search always works, with optional embedding search when a provider is configured.</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -3368,30 +3813,35 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
+          <t>Traceability &amp; knowledge</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
           <t>Change impact analysis</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Walks the traceability graph from a changed artifact to everything downstream of it, across repositories, to show what a change affects before it is accepted.</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -3399,30 +3849,35 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
           <t>Confluence (document store)</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Read and write client Confluence pages as the system of record for documents, with idempotent updates on re-publish.</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>Capability interface — swappable for SharePoint or Drive.</t>
         </is>
@@ -3434,30 +3889,35 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
           <t>Jira (task tracker)</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Epics, stories and sub-tasks, transitions, comments and search against the client's Jira.</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>Sprints deferred.</t>
         </is>
@@ -3469,30 +3929,35 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
           <t>Backlog reconciliation into Jira</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>An approved backlog becomes real Jira issues, registering existing issues rather than recreating them, never duplicating and never rewriting history.</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>Seen live on the fan-out screen, in its unconnected state: 'Task tracker isn't connected, so these live in the platform only. Connect Jira to push them to a backlog.'</t>
         </is>
@@ -3504,30 +3969,35 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
           <t>GitHub (code host)</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Branches, pull requests, file reads, CI status and merges through the client's GitHub, with idempotent PR creation.</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -3535,30 +4005,35 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
           <t>Signed webhook ingestion</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>GitHub webhooks are signature-verified and de-duplicated, then reconciled: a human's push moves the code pointer, a merged PR completes the work item, CI status lands in the ledger.</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>This is how human commits stay tracked.</t>
         </is>
@@ -3570,30 +4045,35 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
           <t>External merge detection</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>A pull request merged directly on GitHub is noticed, and the work item can be closed out in the platform from there.</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -3601,30 +4081,35 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
           <t>Figma (design source)</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Reads the client's Figma file as the design source of truth — frames, variables and components as pointers — and aggregates a design-system artifact plus a design-to-code component mapping.</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>Writing back to the canvas is a deferred seam.</t>
         </is>
@@ -3636,30 +4121,35 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
           <t>Xray (test management)</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Creates test cases in Xray and imports execution results, both idempotent so a re-run updates the same execution rather than duplicating it.</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -3667,30 +4157,35 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
           <t>Built-in code intelligence analyser</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>The default code-analysis engine: churn-and-complexity hotspots, dependency graph and ranking, dead code, ownership and bus factor, and decision history from commits and ADRs — run in the worktree, with only the analysis stored.</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>No third-party analyser required.</t>
         </is>
@@ -3702,30 +4197,35 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
           <t>Rate governor</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>One choke point for all external calls: per-capability rate limiting, jittered backoff on throttling and errors, and a short-lived read cache, so live client tools are not hammered.</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -3733,30 +4233,35 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
           <t>Capability abstraction</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>Agents and services call capabilities (document store, task tracker, code host, design source, test management, code intelligence, accessibility AI), never a vendor, so connectors swap without touching business logic.</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>Locked architecture decision.</t>
         </is>
@@ -3768,30 +4273,35 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
+          <t>Testing &amp; quality</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
           <t>Test cases as tracked work</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Generated test cases are registered artifacts and appear as their own tracked items under a story, reviewable before anything is exported.</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>Seen live: test cases are child work items under a story, addable by hand or generated by the test-automation phase.</t>
         </is>
@@ -3803,30 +4313,35 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
+          <t>Testing &amp; quality</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
           <t>Test case export to Xray</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>An approved test case is exported to the test management tool on demand, keyed so re-export updates the same test rather than creating a second one.</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -3834,30 +4349,35 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
+          <t>Testing &amp; quality</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
           <t>CI test-result ingestion</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>The client's CI posts JUnit results back to the platform with a project CI token; results are recorded, de-duplicated per execution reference, and drive the defect loop.</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>Provider-agnostic — any CI that can emit JUnit.</t>
         </is>
@@ -3869,30 +4389,35 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
+          <t>Testing &amp; quality</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
           <t>Automatic defect loop</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>A failing test opens a defect work item; the same test passing later closes it. Defects are first-class work items, not a separate list.</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -3900,30 +4425,35 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
+          <t>Testing &amp; quality</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
           <t>Flaky test quarantine</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>A test reporting conflicting results in one execution is quarantined and excluded from the blocking gate, instead of randomly failing the pipeline.</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -3931,30 +4461,35 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
+          <t>Testing &amp; quality</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
           <t>Test impact selection</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>Walks the traceability graph from changed code to the tests that cover it, so a change can be verified without running everything.</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -3962,30 +4497,35 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
+          <t>Testing &amp; quality</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
           <t>Testing gate blocks on real failures</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>The QA gate cannot be approved while genuine test failures stand, and quarantined or advisory results are excluded from that judgement.</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
@@ -3993,30 +4533,35 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
           <t>Security review outputs</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>A security run registers a review, one artifact per finding, a threat model and a CycloneDX SBOM, all traceable back to the code and architecture they came from.</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -4024,30 +4569,35 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
           <t>Security defect loop</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Each open critical or high finding becomes a defect work item that closes when the finding is resolved, and the security gate cannot be granted while one is open.</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -4055,30 +4605,35 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
           <t>SBOM view</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>The bill of materials is rendered as a readable table rather than raw JSON, alongside the readable security report.</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -4086,30 +4641,35 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
           <t>Onboarding hub</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>One screen for bringing an existing project onto the platform: upload and adopt documents, register what is in Atlassian, index the code, and read the gap report — each step showing its state.</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>Hidden on greenfield projects.</t>
         </is>
@@ -4121,30 +4681,35 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
           <t>Upload existing specifications</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>Word, PDF, Excel, HTML and text documents are uploaded, stored, and extracted into reviewable content — including embedded images and rendered page images, so nothing pictorial is lost.</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -4152,30 +4717,35 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
           <t>Adopt an uploaded document</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Extraction is lossy and untrusted, so an extracted document only becomes a project artifact when a person adopts it at a gate, with provenance back to the original file.</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -4183,30 +4753,35 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
           <t>Register existing Atlassian content</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>Discovers the project's existing Confluence pages and Jira issues and registers them as-is — never recreating what already exists, and re-running registers nothing new.</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -4214,30 +4789,35 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
           <t>Link specific Confluence pages</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>Point the platform at particular pages and record what kind of artifact each one is, for projects whose documentation is not where discovery would look.</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -4245,30 +4825,35 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
           <t>Run code intelligence on a repository</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>Dispatches the analyser to the developer's machine, and stores the resulting analysis and knowledge index entries — the source code itself is never copied into the platform.</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -4276,30 +4861,35 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
           <t>Gap report</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Assesses every lifecycle phase as complete, partial or missing from the evidence found, names the phase to resume from, and links the evidence behind each verdict.</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
@@ -4307,30 +4897,35 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
+          <t>Brownfield onboarding</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
           <t>Resume mid-pipeline</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>An onboarded project starts at the phase the gap report identified and then runs the same pipeline as any other project — onboarding is not a separate track.</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -4338,30 +4933,35 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
+          <t>API contracts &amp; drift</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
           <t>Versioned API contract</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>One versioned contract per project, exported from the code with semantic versioning, read through by consumers rather than copied, and re-approved at a gate on every version bump.</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
@@ -4369,30 +4969,35 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
+          <t>API contracts &amp; drift</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
           <t>Cross-repository links</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>A consumer in one repository is recorded as implementing a contract in another, and work items can depend on work in a different repository.</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G119" s="6" t="inlineStr"/>
+      <c r="H119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -4400,30 +5005,35 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
+          <t>API contracts &amp; drift</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
           <t>Drift detection</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Notices when a contract has moved past what its consumers implement, or when a read-through artifact no longer matches its recorded hash, and opens a drift review with the impact set.</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>A signed push can open a contract drift review.</t>
         </is>
@@ -4435,30 +5045,35 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
+          <t>API contracts &amp; drift</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
           <t>Drift decision</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>An architect or tech lead accepts drift (reconciling the record) or rejects it (flagging for revert). Nothing is written to a client tool silently either way.</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -4466,30 +5081,35 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
           <t>WCAG 2.2 criterion ownership registry</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>For each of the 55 Level A and AA success criteria, who decides it — the rule engine, the AI, or a person — and what evidence that decision needs. This is what routes every accessibility check.</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G122" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
@@ -4497,30 +5117,35 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
           <t>Rule-engine scan results</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>Automated rule results captured from the running app are turned into platform facts, and a measured rule failure always overrules a contrary AI opinion.</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -4528,30 +5153,35 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
           <t>Screen capture ingestion</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>What a test run saw on each screen — structure, computed styles, accessible names, a full-page image — is posted from the client's CI and stored as the evidence every later check reads.</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
         <is>
           <t>The app under test runs on a machine the server cannot reach.</t>
         </is>
@@ -4563,30 +5193,35 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
           <t>AI accessibility pass</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>Runs the judge agent over captured screens for the criteria no rule engine can settle, and merges its verdicts with the rule results into one report with confidence per finding.</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -4594,30 +5229,35 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
           <t>Confidence triage</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Nothing the AI says reaches a report, a gate or a developer unchecked: low confidence is routed to a human instead of asserted, and the AI can never claim conformance on its own.</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
@@ -4625,30 +5265,35 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
           <t>Brownfield baseline audit</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>Points the engine at an already-built application over a list of routes and produces a full WCAG 2.2 baseline with no prior design phase.</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
         <is>
           <t>Proven on five live runs against a real application.</t>
         </is>
@@ -4660,30 +5305,35 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
           <t>Route registry</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>The list of pages a baseline audit should visit, managed per project, with per-route settings and results.</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr"/>
+      <c r="H128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
@@ -4691,30 +5341,35 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
           <t>Findings ledger with evidence</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>Every finding records the element, the criterion, the reasoning and the screenshot region it describes, on its own page a reviewer can open from anywhere.</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -4722,30 +5377,35 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
           <t>Human review console</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>The queue of findings the checks could not settle, with claim-and-lock so two reviewers never rule on the same item, and a verdict that either clears the finding or raises a defect.</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
           <t>Built - not exercised live</t>
         </is>
       </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
         <is>
           <t>Seen live only in its empty state ('Nothing has been checked yet'). No reviewer has opened a real finding on any project.</t>
         </is>
@@ -4757,30 +5417,35 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
           <t>Accessibility defect loop</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>Accessibility findings open and close tracked defects on their own, the same way test and security findings do, grouped so a page-wide problem is one ticket rather than two hundred.</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -4788,30 +5453,35 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
           <t>Prioritised fix backlog</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>What to fix first for an inherited application with hundreds of findings, ordered by severity and reach, with advisory checks excluded from the blocking set.</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
@@ -4819,30 +5489,35 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
           <t>Coverage accounting</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
+      <c r="D133" s="6" t="inlineStr">
         <is>
           <t>Records what was actually looked at per criterion and per page — not only what was wrong — so an unchecked page never reads as a clean one.</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
         <is>
           <t>Seen live: the conformance screen counts checked vs never-checked separately, so an unchecked criterion cannot read as a passing one.</t>
         </is>
@@ -4854,30 +5529,35 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
           <t>Conformance statement / VPAT</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Compiles the evidence into a statement walking all 55 Level A and AA criteria, drafted from a real audit, signed by a named person, and exported. The platform never certifies on its own.</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
           <t>Built - not signed live</t>
         </is>
       </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>Seen live: all 55 Level A and AA criteria listed with a per-criterion verdict, a Draft-unsigned badge, and 'This is risk reduction, not certification'. Nobody has signed one live yet.</t>
         </is>
@@ -4889,30 +5569,35 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
           <t>Per-project accessibility policy</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="D135" s="6" t="inlineStr">
         <is>
           <t>The target level and which severities block the pipeline, written down where a project owner can read it and an admin can change it, instead of hard-coded.</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -4920,30 +5605,35 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
           <t>Accessibility gate on design</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>The design gate carries the WCAG checklist as gate conditions, so a design cannot be approved while a required criterion is unmet.</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr"/>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
@@ -4951,30 +5641,35 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
+          <t>Platform UI &amp; navigation</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
           <t>Workspace dashboard</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>The landing screen: what needs this person now — gates, questions, reviews — and the health of the project's work, runs and cost.</t>
         </is>
       </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="inlineStr">
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>Seen live: needs-me queue, gates awaiting approval, questions awaiting you, runs in flight, project health and recent publishes.</t>
         </is>
@@ -4986,30 +5681,35 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
+          <t>Platform UI &amp; navigation</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
           <t>Notification badge</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>A live unread count in the top bar and the sidebar, driven by the same needs-me rollup as the dashboard.</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
           <t>Built - partial</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
+      <c r="G138" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>Seen live: the count is real and live, but the bell has no click handler — there is no notification centre behind it.</t>
         </is>
@@ -5021,30 +5721,35 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
+          <t>Platform UI &amp; navigation</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
           <t>Workspace and project switcher</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="D139" s="6" t="inlineStr">
         <is>
           <t>Switch the project in context from the top bar; every screen follows the selection.</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr"/>
+      <c r="H139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -5052,30 +5757,35 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
+          <t>Platform UI &amp; navigation</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
           <t>First-run setup checklist</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>A guided checklist for a new workspace — connect a machine, create a project, connect tools, invite the team — that ticks itself off as each step is genuinely done.</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>Seen live: 4 steps, self-ticking, showing 2 of 4 complete against real workspace state.</t>
         </is>
@@ -5087,30 +5797,35 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
+          <t>Platform UI &amp; navigation</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
           <t>Design system and component library</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="D141" s="6" t="inlineStr">
         <is>
           <t>One shared component library and token set behind every screen, with a developer catalogue page rendering the whole library for parity checks.</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G141" s="6" t="inlineStr"/>
+      <c r="H141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -5118,30 +5833,35 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
+          <t>Platform UI &amp; navigation</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
           <t>Consistent error and empty states</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Failed writes, unavailable previews, empty queues and unauthorised deep links all say what happened and what to do next, rather than failing silently.</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>Seen live throughout, and they are unusually good: each empty state says why it is empty and what would fill it.</t>
         </is>
@@ -5153,37 +5873,726 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
+          <t>Platform UI &amp; navigation</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
           <t>Search and filtering across the registers</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Work items, artifacts, clarification history and gate history each carry a search box and their own filters (phase, level, type, status, role, work item), so a project with hundreds of rows stays navigable.</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Built</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>Seen live on all four registers.</t>
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="11" t="n">
+        <v>144</v>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>Accounts, sign-in &amp; invitations</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Invitation and password-reset emails actually delivered</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>Invitation and password-reset links reach the recipient's inbox. Today they are printed to the server log and an administrator has to copy them out and pass them on by hand.</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="n"/>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 192 (P3). Configuration, not code — the sending code is complete and already called on invitation and on reset. A few hours, most of it verifying a sender with the mail provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>Integrations &amp; connections</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>Integrations per project, not per workspace</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>A connection to Jira, Confluence or a code host can belong to one project rather than the whole workspace, so two projects in the same workspace can use different instances. Workspace-wide connections keep working as the default.</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G145" s="12" t="n"/>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 155 (P3). Best done in four incremental steps so every existing caller keeps working throughout; step one includes a database migration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="n">
+        <v>146</v>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>Integrations &amp; connections</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>Test connection checks the address, not just the credential</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>Test connection resolves the target it was given — the repository, the Jira project key, the Confluence space — and reports it on its own line, instead of only confirming that the credential is real.</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G146" s="12" t="n"/>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 159 (P3). Found live: a repository saved with a stray space passed the test and failed only at the build phase, after a full planning run had been spent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="n">
+        <v>147</v>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>Task breakdown review screen</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>One screen for reviewing a proposed backlog before its gate: the epic-story-task hierarchy, the dependencies between items, and an estimate for each, instead of four plain documents and a separate board.</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G147" s="12" t="n"/>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 75 (P2). Dependencies are already recorded by the backend but read by no screen. Needs an estimate field on the work item — the only part that is not frontend-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="n">
+        <v>148</v>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Edit generated stories and tasks before the gate</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>A reviewer can correct the title, description or level of a story or task the breakdown agent generated, without rejecting the whole gate and re-running the phase.</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G148" s="12" t="n"/>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 76 (P3). The backend edit endpoint is already live and tested; only the form is missing. Editing dependencies or estimates is a later pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="n">
+        <v>149</v>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>Work items</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>Drill from an epic to its stories and tasks</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>An epic lists its stories as links and a story lists its tasks as links, so the tree can be walked from the top. Today each level shows only a count of its children.</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G149" s="12" t="n"/>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 119 (P3). The data is already returned by the lifecycle endpoint, and the panel already exists on the task screen — it needs copying to the epic screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>Phases &amp; runs</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>Only offer the phases that apply to the work item's type</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>The trigger picker offers the phases that make sense for the selected work item's type instead of listing all sixteen — so a test case is offered test automation, not ideation or task breakdown.</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G150" s="12" t="n"/>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 204 (P3). The rules per type need agreeing first. Best held in the phase catalog rather than the picker, so the rule cannot drift between screens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="n">
+        <v>151</v>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>Planning agents</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Overlap guard for work items that touch the same code</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>When planning produces two work items that would build the same file or class, they are either run one after the other or given an agreed interface contract before either branch is started.</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G151" s="12" t="n"/>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 210 (P2). Reproduced: two work items implemented the same three methods with different return contracts, and it surfaced only as a merge conflict. Needs a decision on which of the two shapes to build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="n">
+        <v>152</v>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>Implementation agent asks before it acts</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>The implementation agent raises a clarification when it is genuinely unsure, and asks whether edits should be applied automatically or held for manual review, instead of working only from its brief.</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G152" s="12" t="n"/>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 148 (P3). The row itself asks for this to be reasoned through with the team first. An agent that stops to ask makes builds slower — read alongside the build-duration recon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="n">
+        <v>153</v>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>Build, test &amp; release agents</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>Platform-executed deployment with automatic rollback</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>On approval of the deployment gate the platform performs the deployment itself using the documented strategy, runs the smoke tests, watches the monitoring window and rolls back automatically on any trigger — rather than producing a plan for a person to run.</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G153" s="12" t="n"/>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 196 (P3). The largest item on the enhancement list. Needs a CD-pipeline connector that does not exist yet, and a real target environment, which does not exist yet either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Connect a machine in two clicks (redesign)</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>Enrolling a developer's machine becomes an installable application and a browser approval, replacing the nine manual steps and the pasted token in use today. The person who clicks Approve becomes the machine's owner, which also ends two developers sharing one enrolment record.</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G154" s="12" t="n"/>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 35 (P2) with S.No 138 (P2) folded into it by team decision. Specified in full at docs/CONNECT_MACHINE_REDESIGN_SPEC.md. Roughly 2.5-3 weeks for the first three layers; code signing has a lead time and has to start first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="n">
+        <v>155</v>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>Untrack newly ignored files when a run resumes on an existing branch</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>When a run resumes on a branch an earlier attempt already used, files that a newly added ignore rule now covers are untracked before the first commit — so report binaries committed by that earlier attempt stop re-triggering the code reviewer.</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G155" s="12" t="n"/>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 205 (P3). A manual workaround exists today: close the pull request, delete the branch, and let the phase start a fresh one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="n">
+        <v>156</v>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>The developer's machine</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>Early warning when your connected machine goes offline</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>The run console and the machine status pill say that a connected machine has stopped responding as soon as its heartbeat goes stale, instead of leaving the run looking active until the takeover timeout eventually fails it.</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G156" s="12" t="n"/>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 209 (P3). Observed live: a run sat claimed with no events for over an hour before the timeout fired. The heartbeat and its staleness threshold already exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="n">
+        <v>157</v>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>Clarifications</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Platform checks the agent's risk classification</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>The platform scans an agent's questions and assumptions for the categories that must never be guessed — pricing, compliance, third-party integrations — and promotes any match to a required question before the gate can close, instead of trusting the agent's own labelling.</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G157" s="12" t="n"/>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 164 (P3). A design gap, not an observed failure. Most of the work is agreeing what the never-guess list actually contains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="11" t="n">
+        <v>158</v>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>Artifacts &amp; publishing</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>Edit a generated document while it is still a draft</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>A person can correct a generated document's text while it is a draft held inside the platform, instead of rejecting the gate and re-running a whole phase for one paragraph.</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G158" s="12" t="n"/>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 153 (P3). Must be restricted to drafts that are still internal — letting an edit reach an approved or published document would be a way around a gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="n">
+        <v>159</v>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>Traceability &amp; knowledge</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>Knowledge index populated for greenfield projects</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>Documents are indexed for retrieval when they are published on greenfield projects, the same way brownfield onboarding already indexes them, so agents on those projects can retrieve project knowledge instead of getting nothing back.</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G159" s="12" t="n"/>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 197 (P3). The search engine and the keyword-plus-semantic blend are already built; only the population is unwired. Turning on semantic search is a separate decision with a per-use cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="11" t="n">
+        <v>160</v>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Two-way Jira sync</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>Status changes flow in both directions between the platform and Jira, and issues carry their dependencies, acceptance criteria, story points and design references rather than summary, description and parent alone.</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G160" s="12" t="n"/>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 78 (P2). The code that pushes a status change already exists but is never called; the inbound webhook and the status mapping are the real work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>Connectors to tools of record</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Push selected work items to Jira in context</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>A push action on the task review screen, with a selection step and a confirmation showing exactly what will be sent. Today the push lives on the generic publish screen and sends every proposed work item on the project at once.</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="n"/>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 79 (P2). Depends on the task breakdown review screen (S.No 147 in this file) — plan the two together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="11" t="n">
+        <v>162</v>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Choose what the security scan covers</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>The security trigger opens a chooser offering a specific repository, the project default, or every repository on the project, and starts the scan on that selection. Today it scans one repository and stops with an error on a multi-repo work item that has none pinned.</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="G162" s="12" t="n"/>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>Bugs.xlsx S.No 188 (P3). The flow is already agreed by the team; the chooser needs a mockup before it is built.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G143"/>
+  <autoFilter ref="A1:H162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5194,7 +6603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -5213,7 +6622,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Compiled 9 September 2026 from the source code, the API surface and the React app (docs were cross-checked but the code was treated as the truth). 141 features listed.</t>
+          <t>Compiled 9 September 2026 from the source code, the API surface and the React app (docs were cross-checked but the code was treated as the truth). 142 features listed, plus 19 enhancements added 9 September 2026.</t>
         </is>
       </c>
     </row>
@@ -5230,7 +6639,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Every row here is 'Existing' — a feature that is built and in the product today. 'Enhancement' and 'Based on POC' rows are for the team to add.</t>
+          <t>Existing (142 rows) — a feature that is built and in the product today. Enhancement (19 rows) — agreed work that is not built yet, each carrying its docs/Bugs.xlsx S.No and priority in the comments column so the two registers stay tied together. 'Based on POC' rows are still for the team to add.</t>
         </is>
       </c>
     </row>
@@ -5266,67 +6675,104 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Not built — an enhancement row: agreed work that is specified where a spec exists, and not yet written.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>How central the feature is to the product working end to end — High, Medium or Low. It is not a build order; everything listed is already built.</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>How central the feature is to the product working end to end — High, Medium or Low. It is not a build order. Enhancement rows are deliberately left blank here: everything carrying a priority is already built, and the urgency of an unbuilt item lives in docs/Bugs.xlsx, where the P-numbers mean something different from this column.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Not included</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Anything not yet built: enterprise hardening (secrets vault, segregation of duties, immutable audit, GDPR erasure), cloud runner fleet and sandboxing, alternative engines (Codex/Copilot), DAG parallelism, Slack/Teams notifications, and the monitoring (13) and retrospective (14) agents.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Live check - 9 September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Every screen of the running app was walked signed in as QA_Charlie against the PeopleDesk workspace (252 work items, 89 runs, 370 artifacts). Rows marked 'Seen live' in comments were confirmed with real data; the rest remain source-verified.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Four rows were downgraded by that walk: the lifecycle rail is labelled type-adaptive but renders all 12 phases for every work-item type; run transcripts are never recorded by anything; run cost is never populated on build runs and is shown nowhere; and the notification bell is a badge with no click handler.</t>
+          <t>Every screen of the running app was walked signed in as QA_Charlie against the PeopleDesk workspace (252 work items, 89 runs, 370 artifacts). Rows marked 'Seen live' in comments were confirmed with real data; the rest remain source-verified.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
+          <t>Four rows were downgraded by that walk: the lifecycle rail is labelled type-adaptive but renders all 12 phases for every work-item type; run transcripts are never recorded by anything; run cost is never populated on build runs and is shown nowhere; and the notification bell is a badge with no click handler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
           <t>Not seen live, because this workspace holds one greenfield single-repo project with only GitHub connected: the brownfield onboarding hub, source documents and gap report; accessibility with real findings; API contracts and drift with data; the WCAG criteria checklist on an open design gate; and multi-repo. Those rows stay source-verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Feature and Sub-feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Feature is the main area the row belongs to; Sub-feature is the individual capability, and holds the wording this register was created with — nothing was reworded when the column was added. 25 main features cover all 161 rows. Filter or sort on Feature to read one area at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Numbering</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>S.No 142 does not exist — a row was removed before this file was first committed. The gap is left as it is so that any number already quoted elsewhere still points at the same row. Enhancement rows are numbered from 144.</t>
         </is>
       </c>
     </row>
